--- a/ig/DM-JUILLET-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-JUILLET-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250620120000</t>
+    <t>20250723120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T12:00:00+01:00</t>
+    <t>2025-07-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1602,7 +1602,7 @@
     <t>308</t>
   </si>
   <si>
-    <t>Accompagnements à la parentalité</t>
+    <t>Soutien à la parentalité et accompagnement familial</t>
   </si>
   <si>
     <t>309</t>
